--- a/v0.1.0/BOM-v0.1.0.xlsx
+++ b/v0.1.0/BOM-v0.1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWIFT-EnergyWing\v0.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7B6861-B2D8-4218-B4F2-A9CC84728C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B16225-EFF6-405F-966A-5FFD28C5CC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -80,196 +80,7 @@
     <t>Total Cost (Per Cable)</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/320-1150/10650211</t>
-  </si>
-  <si>
-    <t>A320H (Connector handle)</t>
-  </si>
-  <si>
-    <t>TERM BLADE FEMALE 1/0AWG SILVER</t>
-  </si>
-  <si>
-    <t>320-1150</t>
-  </si>
-  <si>
-    <t>CONN RCPT HSG 2POS</t>
-  </si>
-  <si>
-    <t>8 AWG main contact</t>
-  </si>
-  <si>
-    <t>TERM BLADE NON-GEND 8AWG SILVER</t>
-  </si>
-  <si>
-    <t>1339G5-BK</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/1339G5-BK/10650046</t>
-  </si>
-  <si>
-    <t>Stranded Hookup Wire - Black</t>
-  </si>
-  <si>
-    <t>Stranded Hookup Wire (300 Volt)</t>
-  </si>
-  <si>
-    <t>Wire-ST-16-00-100</t>
-  </si>
-  <si>
-    <t>https://powerwerx.com/stranded-hookup-wire-300volt-ul1007</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/remington-industries/16UL1007STRBLA/11613043</t>
-  </si>
-  <si>
-    <t>Stranded Hookup Wire - Red</t>
-  </si>
-  <si>
-    <t>Wire-ST-16-02-100</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/remington-industries/16UL1007STRRED/11613259</t>
-  </si>
-  <si>
-    <t>8 AWG Red/black Wire</t>
-  </si>
-  <si>
-    <t>Red/Black Bonded Zip Cord Easy ID Low Voltage Cable</t>
-  </si>
-  <si>
-    <t>Wire-RB-08-50</t>
-  </si>
-  <si>
-    <t>https://powerwerx.com/red-black-bonded-zip-cord</t>
-  </si>
-  <si>
-    <t>Mesh Sleeving</t>
-  </si>
-  <si>
-    <t>SLEEVING 0.5" ID POLY 100' BLACK</t>
-  </si>
-  <si>
-    <t>NMN0.50BK100</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/techflex/NMN0-50BK100/2524519</t>
-  </si>
-  <si>
-    <t>8 AWG Ring Terminal</t>
-  </si>
-  <si>
-    <t>CONN RING CIRC 8AWG #8 CRIMP</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0191930200/3044482</t>
-  </si>
-  <si>
-    <t>16 AWG Ring Terminal</t>
-  </si>
-  <si>
-    <t>CONN RING CIRC 14-16AWG #8 CRIMP</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0191930089/3187614</t>
-  </si>
-  <si>
-    <t>Adhesive Lined heat shrink</t>
-  </si>
-  <si>
-    <t>HEATSHRINK 0.752" X 4' BLK 1=1PC</t>
-  </si>
-  <si>
-    <t>Q5-2X-3/4-01-QB48IN-5</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/qualtek/Q5-2X-3-4-01-QB48IN-5/754962</t>
-  </si>
-  <si>
-    <t>LOWER AUX. SOCKET CNT. 14/18 AWG</t>
-  </si>
-  <si>
-    <t>320-23</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/320-23/14551433</t>
-  </si>
-  <si>
-    <t>E320-89</t>
-  </si>
-  <si>
-    <t>320 DIN HANDLE KIT</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/E320-89/14550348</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/320-25/10650279</t>
-  </si>
-  <si>
-    <t>320-25</t>
-  </si>
-  <si>
-    <t>TERM BLADE FEMALE 14-18AWG SILV</t>
-  </si>
-  <si>
-    <t>Main Female Housing</t>
-  </si>
-  <si>
-    <t>A32500-0009</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/A32500-0009/14833308?s=N4IgTCBcDaIIIGYwFYAMqC07UE4QF0BfIA</t>
-  </si>
-  <si>
-    <t>Large Power Contacts</t>
-  </si>
-  <si>
-    <t>Larger Auxiliary Contact</t>
-  </si>
-  <si>
-    <t>Smaller Auxiliary Contact</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/QUICKCABLE-Heat-Shrink-Tubing-0-75-in-64TX48</t>
-  </si>
-  <si>
     <t>Primary or Alternative Part</t>
-  </si>
-  <si>
-    <t>Primary</t>
-  </si>
-  <si>
-    <t>Alternative</t>
-  </si>
-  <si>
-    <t>QUICKCABLE Heat Shrink Tubing: 0.75 in I.D. Before Shrinking, 0.25 in I.D. After Shrinking, 5 PK</t>
-  </si>
-  <si>
-    <t>5662-005B</t>
-  </si>
-  <si>
-    <t>Precut to 6" which can be nice</t>
-  </si>
-  <si>
-    <t>8 AWG Red Wire</t>
-  </si>
-  <si>
-    <t>8 AWG Black Wire</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/cnc-tech/3132-8-1-0100-004-1-TS/25587759</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/cnc-tech/3132-8-1-0100-001-1-TS/25587757</t>
-  </si>
-  <si>
-    <t>3132-8-1-0100-001-1-TS</t>
-  </si>
-  <si>
-    <t>3132-8-1-0100-004-1-TS</t>
-  </si>
-  <si>
-    <t>UL3132, SILICONE WIRE, 8AWG, RED</t>
   </si>
 </sst>
 </file>
@@ -783,29 +594,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="27.265625" customWidth="1"/>
+    <col min="3" max="3" width="37.86328125" customWidth="1"/>
+    <col min="4" max="4" width="20.73046875" customWidth="1"/>
+    <col min="5" max="5" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="79" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.42578125" customWidth="1"/>
-    <col min="12" max="12" width="62.42578125" customWidth="1"/>
-    <col min="13" max="13" width="55.85546875" customWidth="1"/>
+    <col min="10" max="10" width="45.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.3984375" customWidth="1"/>
+    <col min="12" max="12" width="62.3984375" customWidth="1"/>
+    <col min="13" max="13" width="55.86328125" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>11</v>
@@ -844,479 +655,198 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="19">
-        <v>2</v>
-      </c>
-      <c r="F2" s="9">
-        <v>30.75</v>
-      </c>
-      <c r="G2" s="9">
-        <f>E2*F2</f>
-        <v>61.5</v>
-      </c>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I2" s="1"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="9">
-        <v>8.51</v>
-      </c>
-      <c r="G3" s="9">
-        <f>E3*F3</f>
-        <v>8.51</v>
-      </c>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="19">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9">
-        <v>11.25</v>
-      </c>
-      <c r="G4" s="9">
-        <f t="shared" ref="G4" si="0">E4*F4</f>
-        <v>22.5</v>
-      </c>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="17"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="21" t="s">
-        <v>55</v>
-      </c>
+      <c r="I4" s="21"/>
       <c r="J4" s="4"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="19">
-        <v>2</v>
-      </c>
-      <c r="F5" s="9">
-        <v>14</v>
-      </c>
-      <c r="G5" s="9">
-        <f t="shared" ref="G5" si="1">E5*F5</f>
-        <v>28</v>
-      </c>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="17"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="9">
-        <v>2.72</v>
-      </c>
-      <c r="G6" s="9">
-        <f>F6*E6</f>
-        <v>5.44</v>
-      </c>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="17"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9">
-        <v>12.54</v>
-      </c>
-      <c r="G7" s="9">
-        <f t="shared" ref="G7:G11" si="2">F7*E7</f>
-        <v>12.54</v>
-      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="10"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9">
-        <v>12.54</v>
-      </c>
-      <c r="G8" s="9">
-        <f t="shared" si="2"/>
-        <v>12.54</v>
-      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="10"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9">
-        <v>128.19</v>
-      </c>
-      <c r="G9" s="9">
-        <f t="shared" si="2"/>
-        <v>128.19</v>
-      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="2"/>
-        <v>22.400000000000002</v>
-      </c>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="10"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="I10" s="1"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5</v>
-      </c>
-      <c r="F11" s="9">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="2"/>
-        <v>22.400000000000002</v>
-      </c>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="10"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="I11" s="1"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="24">
-        <v>1</v>
-      </c>
-      <c r="F12" s="26">
-        <v>72.62</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" ref="G12:G17" si="3">E12*F12</f>
-        <v>72.62</v>
-      </c>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="22"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="27"/>
-      <c r="I12" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="20">
-        <v>191930200</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="10"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="16">
-        <v>191930089</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0.42</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" si="3"/>
-        <v>0.84</v>
-      </c>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="10"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9">
-        <v>6.22</v>
-      </c>
-      <c r="G15" s="9">
-        <f t="shared" si="3"/>
-        <v>6.22</v>
-      </c>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>12.94</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="3"/>
-        <v>12.94</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="10"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>23.22</v>
-      </c>
-      <c r="G17" s="9">
-        <f t="shared" si="3"/>
-        <v>23.22</v>
-      </c>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="10"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="I17" s="3"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1329,7 +859,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1341,7 +871,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1352,42 +882,22 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="F22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G22" s="5">
         <f>SUM(G2:G21)</f>
-        <v>440.86</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{47569AE6-6AA0-4875-B93F-ACB3A5943EC4}"/>
-    <hyperlink ref="I9" r:id="rId2" xr:uid="{29C65987-503D-4D38-A3A8-F300B92B5979}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{D49830EC-B643-4C9C-A66A-316B6E8D393B}"/>
-    <hyperlink ref="J7" r:id="rId4" xr:uid="{DB6CFF9E-0CFE-4630-97DC-2259E72BBA6B}"/>
-    <hyperlink ref="J8" r:id="rId5" xr:uid="{7F0A5667-B170-4E9F-A116-7812C5481D5D}"/>
-    <hyperlink ref="I7" r:id="rId6" xr:uid="{47AB98CE-DF5D-4668-ABC4-20DA7A425CBD}"/>
-    <hyperlink ref="I8" r:id="rId7" xr:uid="{FE305D2A-720D-4EAC-A689-433507294DC8}"/>
-    <hyperlink ref="I12" r:id="rId8" xr:uid="{4AF02486-862F-4C90-B472-12C65FB0F86D}"/>
-    <hyperlink ref="I13" r:id="rId9" xr:uid="{60DC3860-834C-416B-A80D-912D2A7218E7}"/>
-    <hyperlink ref="I14" r:id="rId10" xr:uid="{DEEF517E-6B30-41FE-90B5-BDD5F67AF727}"/>
-    <hyperlink ref="I15" r:id="rId11" xr:uid="{F28C2672-213B-4C58-924E-5743A03E60B9}"/>
-    <hyperlink ref="I5" r:id="rId12" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
-    <hyperlink ref="I3" r:id="rId13" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
-    <hyperlink ref="I4" r:id="rId14" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
-    <hyperlink ref="I17" r:id="rId15" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
-    <hyperlink ref="I16" r:id="rId16" xr:uid="{33EA6662-3BF5-4567-9053-50ED0DB9E78A}"/>
-    <hyperlink ref="I10" r:id="rId17" xr:uid="{481207C2-2276-4195-833B-5B8F0CF49279}"/>
-    <hyperlink ref="I11" r:id="rId18" xr:uid="{9A6ACCBE-7885-4833-B391-4A619D41B841}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/v0.1.0/BOM-v0.1.0.xlsx
+++ b/v0.1.0/BOM-v0.1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/cpennese_email_sc_edu/Documents/Attachments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWIFT-EnergyWing\v0.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DCA2A85-FF07-4C7E-8A7E-D6496C3902C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF90740-41B6-4035-A739-89FF4CA2BF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{B9911C6F-0B58-40F6-BAF9-4BEDC7DF3945}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9911C6F-0B58-40F6-BAF9-4BEDC7DF3945}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="80">
   <si>
     <t>Internal Part Name</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Material type</t>
   </si>
   <si>
-    <t>MFR / Vendor Description</t>
-  </si>
-  <si>
     <t>MFR Part Number</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Machine</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>BVV2G-RT</t>
   </si>
   <si>
@@ -221,17 +215,77 @@
     <t>https://fiberglassflorida.com/general-purpose-epoxy-2-1.html</t>
   </si>
   <si>
-    <t>Fiber glass Florida has insanely long descriptions</t>
-  </si>
-  <si>
     <t>Total:</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Professional Resin Degassing Chamber Kit: 3.5CFM Pump &amp; 3Gal Stainless Steel Pot for Bubble Removal</t>
+  </si>
+  <si>
+    <t>VP125</t>
+  </si>
+  <si>
+    <t>(BVV Trap)</t>
+  </si>
+  <si>
+    <t>(Trap &amp; Vacuum)</t>
+  </si>
+  <si>
+    <t>5 Gallon Acrylic Vacuum Chamber 3.5 CFM Pump Epoxy Resin Degassing Pot 304 SS XL</t>
+  </si>
+  <si>
+    <t>VH1365US-N1</t>
+  </si>
+  <si>
+    <t>(Big trap kit)</t>
+  </si>
+  <si>
+    <t>Resin Trap and vacuum (similar to the one at maher they said the trap was great but the vacuum was subpar)</t>
+  </si>
+  <si>
+    <t>Resin Trap and Vacuum and oil and and tubing</t>
+  </si>
+  <si>
+    <t>Resin Trap for protecting  pump and holding vacuum</t>
+  </si>
+  <si>
+    <t>Tube connector Dr. Mobli's lab uses (rips bag less)</t>
+  </si>
+  <si>
+    <t>misc</t>
+  </si>
+  <si>
+    <t>Consumable for easier removal of DM</t>
+  </si>
+  <si>
+    <t>Consumable for distribution of resin during vacuum</t>
+  </si>
+  <si>
+    <t>Vacuum bag material (keeps air out)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box of 100 gloves </t>
+  </si>
+  <si>
+    <t>Restock on mixing cups</t>
+  </si>
+  <si>
+    <t>Same resin system that was used before</t>
+  </si>
+  <si>
+    <t>https://www.walmart.com/ip/Professional-Resin-Degassing-Chamber-Kit-3-5CFM-Pump-3Gal-Stainless-Steel-Pot-for-Bubble-Removal/17634851034?wmlspartner=wlpa&amp;selectedSellerId=102879550&amp;selectedOfferId=8423975386863AD483C2ADC23C47CB0A&amp;conditionGroupCode=1&amp;veh=seo_fpl&amp;cn=google</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/298685076596?_trkparms=itmf%3D1%26aid%3D1110018%26rkt%3D12%26pid%3D101196%26mech%3D1%26algv%3DCompVIDesktopATF2V6ReplaceKnnV4WithVectorDbNsOptHotPlRecallWithSiblingFilterCpcRecallsWithCiiQueryEmbedding%26pmt%3D1%26amclksrc%3DITM%26sd%3D274055133119%26sid%3DAQALAAAAEBhifTdfkzmTeD29moLFtbQ%3D%26itm%3D298685076596%26noa%3D0%26plcampt%3D0%3A168365155016%26algo%3DHOMESPLICE.COMPLISTINGS%26brand%3DUnbranded%26asc%3D344877,344812%26ao%3D1%26rk%3D4%26mehot%3Dpf%26lsid%3D0%26meid%3D06a96f6edf5e4eecbc4511079969d9f8%26pg%3D2332490&amp;_trksid=p2332490.c101196.m2219&amp;itmprp=cksum%3A29868507659606a96f6edf5e4eecbc4511079969d9f8%7Cenc%3AAQALAAABYPc4YgTWUogX4l4Wo4r6rbj89PpwuaernzlZ%252BQ9Jflnere4td0FNO7ZUFpdCZ5W1PHVcKr90xHJ8HZYqTb2OAMqpJmPfQb42ATbkA3%252F%252B2uHBZ%252FYS0K3D8IU17hUyYNcxbIlqG%252FrH0utxChRg1mB7bHXQX%252Fk5fmf5TAJ%252FOIK%252BRPgzS8YY5xe36qx6wNxEzq%252BK0cnZciiiEFfQLkdLE6PFi9YOm3XRxQmrv31OQX4j6%252FLl7wRe3Gfdi8b959nWJAdZlZyv2Wv1%252B3qUFZTCfswyxdUHTeunuZi%252F2xMob%252Fn5ea0NyW8Z1oEAGUMbpW%252Be0O50fUdmBeycFTuUrC5C%252BohHu7JrNOORena6hqfbDvuIRaAbaPMmKrcHpzZOSuZwovCMtBdL2xk80MPzwPM24CM3hTekJ2WSXh9PLwM5OCzndnvjmv8cEMpMYIYqNwTnrqzmzJRfOqaM6K%252BfTEY8Hse%252BoP4%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01M3XM7EJPTMJSFBDZ6C6AAH7P</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,7 +355,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -318,16 +374,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -663,19 +722,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C4AB73-3D58-471D-94BA-BB655CD96E29}">
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
     <col min="3" max="3" width="41.7109375" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" customWidth="1"/>
     <col min="5" max="5" width="24.140625" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,54 +743,54 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -742,24 +802,24 @@
         <v>141.94999999999999</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>27.25</v>
@@ -768,24 +828,24 @@
         <v>27.25</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
       </c>
       <c r="F4">
         <v>12.76</v>
@@ -794,18 +854,21 @@
         <v>38.28</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -817,21 +880,24 @@
         <v>10.35</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
+      <c r="E6" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
       </c>
       <c r="F6">
         <v>7.45</v>
@@ -840,21 +906,24 @@
         <v>22.35</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>4.41</v>
@@ -863,21 +932,24 @@
         <v>13.23</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
+      <c r="E8" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
       </c>
       <c r="F8">
         <v>9.81</v>
@@ -886,21 +958,24 @@
         <v>49.05</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
       </c>
       <c r="F9">
         <v>10.88</v>
@@ -909,24 +984,27 @@
         <v>10.88</v>
       </c>
       <c r="H9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
+      <c r="E10" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
       </c>
       <c r="F10">
         <v>0.56000000000000005</v>
@@ -936,21 +1014,24 @@
         <v>16.8</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
+      <c r="E11" t="s">
         <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>57</v>
       </c>
       <c r="F11">
         <v>46.63</v>
@@ -959,22 +1040,92 @@
         <v>46.63</v>
       </c>
       <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12">
+        <v>129.88</v>
+      </c>
+      <c r="G12">
+        <v>129.88</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>115.99</v>
+      </c>
+      <c r="G13">
+        <v>115.99</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G15" s="5">
         <f>G2+G3+G4+G5+G7+G6+G8+G9+G10+G11</f>
         <v>376.77</v>
+      </c>
+      <c r="H15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G16" s="5">
+        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12</f>
+        <v>364.7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G17" s="5">
+        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G13</f>
+        <v>350.81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +1140,303 @@
     <hyperlink ref="I9" r:id="rId8" xr:uid="{5E11E40F-DA71-4724-9E02-158766486D67}"/>
     <hyperlink ref="I10" r:id="rId9" xr:uid="{2EE44D3D-C25B-43B1-B76A-2CE7336F6FB3}"/>
     <hyperlink ref="I11" r:id="rId10" xr:uid="{B1C12278-1783-4746-9111-56931CBC31ED}"/>
+    <hyperlink ref="I12" r:id="rId11" display="https://www.walmart.com/ip/Professional-Resin-Degassing-Chamber-Kit-3-5CFM-Pump-3Gal-Stainless-Steel-Pot-for-Bubble-Removal/17634851034?wmlspartner=wlpa&amp;selectedSellerId=102879550&amp;selectedOfferId=8423975386863AD483C2ADC23C47CB0A&amp;conditionGroupCode=1&amp;veh=seo_fpl&amp;cn=google" xr:uid="{DAFB3B20-2997-49B5-B493-559F6770C825}"/>
+    <hyperlink ref="I13" r:id="rId12" display="https://www.ebay.com/itm/298685076596?_trkparms=itmf%3D1%26aid%3D1110018%26rkt%3D12%26pid%3D101196%26mech%3D1%26algv%3DCompVIDesktopATF2V6ReplaceKnnV4WithVectorDbNsOptHotPlRecallWithSiblingFilterCpcRecallsWithCiiQueryEmbedding%26pmt%3D1%26amclksrc%3DITM%26sd%3D274055133119%26sid%3DAQALAAAAEBhifTdfkzmTeD29moLFtbQ%3D%26itm%3D298685076596%26noa%3D0%26plcampt%3D0%3A168365155016%26algo%3DHOMESPLICE.COMPLISTINGS%26brand%3DUnbranded%26asc%3D344877,344812%26ao%3D1%26rk%3D4%26mehot%3Dpf%26lsid%3D0%26meid%3D06a96f6edf5e4eecbc4511079969d9f8%26pg%3D2332490&amp;_trksid=p2332490.c101196.m2219&amp;itmprp=cksum%3A29868507659606a96f6edf5e4eecbc4511079969d9f8%7Cenc%3AAQALAAABYPc4YgTWUogX4l4Wo4r6rbj89PpwuaernzlZ%252BQ9Jflnere4td0FNO7ZUFpdCZ5W1PHVcKr90xHJ8HZYqTb2OAMqpJmPfQb42ATbkA3%252F%252B2uHBZ%252FYS0K3D8IU17hUyYNcxbIlqG%252FrH0utxChRg1mB7bHXQX%252Fk5fmf5TAJ%252FOIK%252BRPgzS8YY5xe36qx6wNxEzq%252BK0cnZciiiEFfQLkdLE6PFi9YOm3XRxQmrv31OQX4j6%252FLl7wRe3Gfdi8b959nWJAdZlZyv2Wv1%252B3qUFZTCfswyxdUHTeunuZi%252F2xMob%252Fn5ea0NyW8Z1oEAGUMbpW%252Be0O50fUdmBeycFTuUrC5C%252BohHu7JrNOORena6hqfbDvuIRaAbaPMmKrcHpzZOSuZwovCMtBdL2xk80MPzwPM24CM3hTekJ2WSXh9PLwM5OCzndnvjmv8cEMpMYIYqNwTnrqzmzJRfOqaM6K%252BfTEY8Hse%252BoP4%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01M3XM7EJPTMJSFBDZ6C6AAH7P" xr:uid="{4501576A-3AB9-4C76-BB45-4140C6D8F244}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C87E5514EFE65F4E8BD4F79E5700A271" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd4488ac6ff5d5fed6befb16a0157598">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xmlns:ns4="1d83a163-44bc-4e6e-b6b0-ecb43fc9c791" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5566a0e904ddb0beb6ef32b558e35e53" ns3:_="" ns4:_="">
+    <xsd:import namespace="9198b1fd-358e-45fb-bdf7-f7260f8bea38"/>
+    <xsd:import namespace="1d83a163-44bc-4e6e-b6b0-ecb43fc9c791"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9198b1fd-358e-45fb-bdf7-f7260f8bea38" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="11" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="15" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="16" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="20" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1d83a163-44bc-4e6e-b6b0-ecb43fc9c791" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="14" nillable="true" ma:displayName="Sharing Hint Hash" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CE2F73F-AE9C-4F09-87BB-63FF8CFD5709}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9198b1fd-358e-45fb-bdf7-f7260f8bea38"/>
+    <ds:schemaRef ds:uri="1d83a163-44bc-4e6e-b6b0-ecb43fc9c791"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24776F69-5EC1-447F-A36A-EC9723B33E80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9198b1fd-358e-45fb-bdf7-f7260f8bea38"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="1d83a163-44bc-4e6e-b6b0-ecb43fc9c791"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C91886-5DA0-4E68-9B51-063847DFF951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/v0.1.0/BOM-v0.1.0.xlsx
+++ b/v0.1.0/BOM-v0.1.0.xlsx
@@ -1381,20 +1381,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1417,6 +1417,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C91886-5DA0-4E68-9B51-063847DFF951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24776F69-5EC1-447F-A36A-EC9723B33E80}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1431,12 +1439,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C91886-5DA0-4E68-9B51-063847DFF951}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/v0.1.0/BOM-v0.1.0.xlsx
+++ b/v0.1.0/BOM-v0.1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\SWIFT-EnergyWing\v0.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF90740-41B6-4035-A739-89FF4CA2BF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99107508-5B48-4D91-9083-95D266987276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9911C6F-0B58-40F6-BAF9-4BEDC7DF3945}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B9911C6F-0B58-40F6-BAF9-4BEDC7DF3945}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
   <si>
     <t>Internal Part Name</t>
   </si>
@@ -209,9 +209,6 @@
     <t>1 kit</t>
   </si>
   <si>
-    <t>Quart Kit</t>
-  </si>
-  <si>
     <t>https://fiberglassflorida.com/general-purpose-epoxy-2-1.html</t>
   </si>
   <si>
@@ -221,33 +218,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Professional Resin Degassing Chamber Kit: 3.5CFM Pump &amp; 3Gal Stainless Steel Pot for Bubble Removal</t>
-  </si>
-  <si>
-    <t>VP125</t>
-  </si>
-  <si>
-    <t>(BVV Trap)</t>
-  </si>
-  <si>
-    <t>(Trap &amp; Vacuum)</t>
-  </si>
-  <si>
-    <t>5 Gallon Acrylic Vacuum Chamber 3.5 CFM Pump Epoxy Resin Degassing Pot 304 SS XL</t>
-  </si>
-  <si>
-    <t>VH1365US-N1</t>
-  </si>
-  <si>
-    <t>(Big trap kit)</t>
-  </si>
-  <si>
-    <t>Resin Trap and vacuum (similar to the one at maher they said the trap was great but the vacuum was subpar)</t>
-  </si>
-  <si>
-    <t>Resin Trap and Vacuum and oil and and tubing</t>
-  </si>
-  <si>
     <t>Resin Trap for protecting  pump and holding vacuum</t>
   </si>
   <si>
@@ -275,10 +245,10 @@
     <t>Same resin system that was used before</t>
   </si>
   <si>
-    <t>https://www.walmart.com/ip/Professional-Resin-Degassing-Chamber-Kit-3-5CFM-Pump-3Gal-Stainless-Steel-Pot-for-Bubble-Removal/17634851034?wmlspartner=wlpa&amp;selectedSellerId=102879550&amp;selectedOfferId=8423975386863AD483C2ADC23C47CB0A&amp;conditionGroupCode=1&amp;veh=seo_fpl&amp;cn=google</t>
-  </si>
-  <si>
-    <t>https://www.ebay.com/itm/298685076596?_trkparms=itmf%3D1%26aid%3D1110018%26rkt%3D12%26pid%3D101196%26mech%3D1%26algv%3DCompVIDesktopATF2V6ReplaceKnnV4WithVectorDbNsOptHotPlRecallWithSiblingFilterCpcRecallsWithCiiQueryEmbedding%26pmt%3D1%26amclksrc%3DITM%26sd%3D274055133119%26sid%3DAQALAAAAEBhifTdfkzmTeD29moLFtbQ%3D%26itm%3D298685076596%26noa%3D0%26plcampt%3D0%3A168365155016%26algo%3DHOMESPLICE.COMPLISTINGS%26brand%3DUnbranded%26asc%3D344877,344812%26ao%3D1%26rk%3D4%26mehot%3Dpf%26lsid%3D0%26meid%3D06a96f6edf5e4eecbc4511079969d9f8%26pg%3D2332490&amp;_trksid=p2332490.c101196.m2219&amp;itmprp=cksum%3A29868507659606a96f6edf5e4eecbc4511079969d9f8%7Cenc%3AAQALAAABYPc4YgTWUogX4l4Wo4r6rbj89PpwuaernzlZ%252BQ9Jflnere4td0FNO7ZUFpdCZ5W1PHVcKr90xHJ8HZYqTb2OAMqpJmPfQb42ATbkA3%252F%252B2uHBZ%252FYS0K3D8IU17hUyYNcxbIlqG%252FrH0utxChRg1mB7bHXQX%252Fk5fmf5TAJ%252FOIK%252BRPgzS8YY5xe36qx6wNxEzq%252BK0cnZciiiEFfQLkdLE6PFi9YOm3XRxQmrv31OQX4j6%252FLl7wRe3Gfdi8b959nWJAdZlZyv2Wv1%252B3qUFZTCfswyxdUHTeunuZi%252F2xMob%252Fn5ea0NyW8Z1oEAGUMbpW%252Be0O50fUdmBeycFTuUrC5C%252BohHu7JrNOORena6hqfbDvuIRaAbaPMmKrcHpzZOSuZwovCMtBdL2xk80MPzwPM24CM3hTekJ2WSXh9PLwM5OCzndnvjmv8cEMpMYIYqNwTnrqzmzJRfOqaM6K%252BfTEY8Hse%252BoP4%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01M3XM7EJPTMJSFBDZ6C6AAH7P</t>
+    <t>Quart Kit - Medium</t>
+  </si>
+  <si>
+    <t>1/2 inch</t>
   </si>
 </sst>
 </file>
@@ -310,21 +280,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -341,34 +305,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -380,13 +316,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -723,19 +659,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C4AB73-3D58-471D-94BA-BB655CD96E29}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="39.265625" customWidth="1"/>
+    <col min="2" max="2" width="24.265625" customWidth="1"/>
+    <col min="3" max="3" width="41.73046875" customWidth="1"/>
+    <col min="4" max="4" width="24.265625" customWidth="1"/>
+    <col min="5" max="5" width="24.1328125" customWidth="1"/>
+    <col min="6" max="6" width="19.3984375" customWidth="1"/>
+    <col min="7" max="7" width="20.265625" customWidth="1"/>
+    <col min="8" max="8" width="15.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -779,7 +715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -787,7 +723,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -805,7 +741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -831,7 +767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -857,15 +793,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -879,11 +815,14 @@
       <c r="G5">
         <v>10.35</v>
       </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
       <c r="I5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -891,7 +830,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -909,7 +848,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -917,7 +856,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
@@ -935,7 +874,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -943,7 +882,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -961,7 +900,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -969,7 +908,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -990,7 +929,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -998,7 +937,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -1017,7 +956,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1025,7 +964,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1040,93 +979,45 @@
         <v>46.63</v>
       </c>
       <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A13" s="3"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="F15" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12">
-        <v>129.88</v>
-      </c>
-      <c r="G12">
-        <v>129.88</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13">
-        <v>115.99</v>
-      </c>
-      <c r="G13">
-        <v>115.99</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <f>G2+G3+G4+G5+G7+G6+G8+G9+G10+G11</f>
         <v>376.77</v>
       </c>
-      <c r="H15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G16" s="5">
-        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12</f>
-        <v>364.7</v>
-      </c>
-      <c r="H16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G17" s="5">
-        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G13</f>
-        <v>350.81</v>
-      </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.45">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1140,8 +1031,6 @@
     <hyperlink ref="I9" r:id="rId8" xr:uid="{5E11E40F-DA71-4724-9E02-158766486D67}"/>
     <hyperlink ref="I10" r:id="rId9" xr:uid="{2EE44D3D-C25B-43B1-B76A-2CE7336F6FB3}"/>
     <hyperlink ref="I11" r:id="rId10" xr:uid="{B1C12278-1783-4746-9111-56931CBC31ED}"/>
-    <hyperlink ref="I12" r:id="rId11" display="https://www.walmart.com/ip/Professional-Resin-Degassing-Chamber-Kit-3-5CFM-Pump-3Gal-Stainless-Steel-Pot-for-Bubble-Removal/17634851034?wmlspartner=wlpa&amp;selectedSellerId=102879550&amp;selectedOfferId=8423975386863AD483C2ADC23C47CB0A&amp;conditionGroupCode=1&amp;veh=seo_fpl&amp;cn=google" xr:uid="{DAFB3B20-2997-49B5-B493-559F6770C825}"/>
-    <hyperlink ref="I13" r:id="rId12" display="https://www.ebay.com/itm/298685076596?_trkparms=itmf%3D1%26aid%3D1110018%26rkt%3D12%26pid%3D101196%26mech%3D1%26algv%3DCompVIDesktopATF2V6ReplaceKnnV4WithVectorDbNsOptHotPlRecallWithSiblingFilterCpcRecallsWithCiiQueryEmbedding%26pmt%3D1%26amclksrc%3DITM%26sd%3D274055133119%26sid%3DAQALAAAAEBhifTdfkzmTeD29moLFtbQ%3D%26itm%3D298685076596%26noa%3D0%26plcampt%3D0%3A168365155016%26algo%3DHOMESPLICE.COMPLISTINGS%26brand%3DUnbranded%26asc%3D344877,344812%26ao%3D1%26rk%3D4%26mehot%3Dpf%26lsid%3D0%26meid%3D06a96f6edf5e4eecbc4511079969d9f8%26pg%3D2332490&amp;_trksid=p2332490.c101196.m2219&amp;itmprp=cksum%3A29868507659606a96f6edf5e4eecbc4511079969d9f8%7Cenc%3AAQALAAABYPc4YgTWUogX4l4Wo4r6rbj89PpwuaernzlZ%252BQ9Jflnere4td0FNO7ZUFpdCZ5W1PHVcKr90xHJ8HZYqTb2OAMqpJmPfQb42ATbkA3%252F%252B2uHBZ%252FYS0K3D8IU17hUyYNcxbIlqG%252FrH0utxChRg1mB7bHXQX%252Fk5fmf5TAJ%252FOIK%252BRPgzS8YY5xe36qx6wNxEzq%252BK0cnZciiiEFfQLkdLE6PFi9YOm3XRxQmrv31OQX4j6%252FLl7wRe3Gfdi8b959nWJAdZlZyv2Wv1%252B3qUFZTCfswyxdUHTeunuZi%252F2xMob%252Fn5ea0NyW8Z1oEAGUMbpW%252Be0O50fUdmBeycFTuUrC5C%252BohHu7JrNOORena6hqfbDvuIRaAbaPMmKrcHpzZOSuZwovCMtBdL2xk80MPzwPM24CM3hTekJ2WSXh9PLwM5OCzndnvjmv8cEMpMYIYqNwTnrqzmzJRfOqaM6K%252BfTEY8Hse%252BoP4%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01M3XM7EJPTMJSFBDZ6C6AAH7P" xr:uid="{4501576A-3AB9-4C76-BB45-4140C6D8F244}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1381,20 +1270,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9198b1fd-358e-45fb-bdf7-f7260f8bea38" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1417,14 +1306,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C91886-5DA0-4E68-9B51-063847DFF951}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24776F69-5EC1-447F-A36A-EC9723B33E80}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1439,4 +1320,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C91886-5DA0-4E68-9B51-063847DFF951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>